--- a/outputs/55260.xlsx
+++ b/outputs/55260.xlsx
@@ -105,11 +105,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,7 +317,7 @@
         <v>367.5</v>
       </c>
       <c r="C1" s="2" t="n">
-        <f aca="false">IF(MOD(B1,5)=2.5, FLOOR(B1,5), MROUND(B1,5))</f>
+        <f aca="false">CEILING(B1/5-0.5,1)*5</f>
         <v>365</v>
       </c>
     </row>
@@ -330,7 +330,7 @@
         <v>498.75</v>
       </c>
       <c r="C2" s="2" t="n">
-        <f aca="false">IF(MOD(B2,5)=2.5, FLOOR(B2,5), MROUND(B2,5))</f>
+        <f aca="false">CEILING(B2/5-0.5,1)*5</f>
         <v>500</v>
       </c>
     </row>

--- a/outputs/55260.xlsx
+++ b/outputs/55260.xlsx
@@ -317,7 +317,7 @@
         <v>367.5</v>
       </c>
       <c r="C1" s="2" t="n">
-        <f aca="false">CEILING(B1/5-0.5,1)*5</f>
+        <f aca="false">IF(MOD(B1,5)=2.5,ROUND(B1,-1)-5,ROUND(B1,-1))</f>
         <v>365</v>
       </c>
     </row>
@@ -330,7 +330,7 @@
         <v>498.75</v>
       </c>
       <c r="C2" s="2" t="n">
-        <f aca="false">CEILING(B2/5-0.5,1)*5</f>
+        <f aca="false">IF(MOD(B2,5)=2.5,ROUND(B2,-1)-5,ROUND(B2,-1))</f>
         <v>500</v>
       </c>
     </row>
